--- a/artfynd/A 47321-2023 artfynd.xlsx
+++ b/artfynd/A 47321-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121942850</v>
       </c>
       <c r="B2" t="n">
-        <v>57726</v>
+        <v>57734</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47321-2023 artfynd.xlsx
+++ b/artfynd/A 47321-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121942850</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>57738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47321-2023 artfynd.xlsx
+++ b/artfynd/A 47321-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121942850</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57742</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47321-2023 artfynd.xlsx
+++ b/artfynd/A 47321-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121942850</v>
       </c>
       <c r="B2" t="n">
-        <v>57742</v>
+        <v>57744</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47321-2023 artfynd.xlsx
+++ b/artfynd/A 47321-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>130322560</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>57979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>130322558</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47321-2023 artfynd.xlsx
+++ b/artfynd/A 47321-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>130322560</v>
       </c>
       <c r="B3" t="n">
-        <v>57979</v>
+        <v>57981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>130322558</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47321-2023 artfynd.xlsx
+++ b/artfynd/A 47321-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>130322560</v>
       </c>
       <c r="B3" t="n">
-        <v>57981</v>
+        <v>57989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>130322558</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47321-2023 artfynd.xlsx
+++ b/artfynd/A 47321-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>130322560</v>
       </c>
       <c r="B3" t="n">
-        <v>57989</v>
+        <v>57990</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>130322558</v>
       </c>
       <c r="B4" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47321-2023 artfynd.xlsx
+++ b/artfynd/A 47321-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>130322560</v>
       </c>
       <c r="B3" t="n">
-        <v>57990</v>
+        <v>57991</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>130322558</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47321-2023 artfynd.xlsx
+++ b/artfynd/A 47321-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121942850</v>
+        <v>130322558</v>
       </c>
       <c r="B2" t="n">
-        <v>57744</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -753,12 +748,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,37 +790,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130322560</v>
+        <v>121942850</v>
       </c>
       <c r="B3" t="n">
-        <v>57991</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103035</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -858,22 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>08:37</t>
+          <t>2025-01-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:03</t>
+          <t>2025-01-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,32 +895,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130322558</v>
+        <v>130322560</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>58082</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103035</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 47321-2023 artfynd.xlsx
+++ b/artfynd/A 47321-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130322558</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121942850</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,8 +1022,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130322560</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>